--- a/output/Daily_Route_Summary_cross.xlsx
+++ b/output/Daily_Route_Summary_cross.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,40 +424,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>driver_label</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>stop_count</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>stop_count</t>
+          <t>service_min</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>service_min</t>
+          <t>drive_min</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>drive_min</t>
+          <t>dist_km</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dist_km</t>
+          <t>total_min</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>total_min</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>overtime_min</t>
         </is>
@@ -469,31 +464,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>424</v>
       </c>
       <c r="E2" t="n">
-        <v>296</v>
+        <v>413.61</v>
       </c>
       <c r="F2" t="n">
-        <v>232.99</v>
+        <v>241.27</v>
       </c>
       <c r="G2" t="n">
-        <v>135.91</v>
+        <v>837.61</v>
       </c>
       <c r="H2" t="n">
-        <v>528.99</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
+        <v>297.61</v>
       </c>
     </row>
     <row r="3">
@@ -502,31 +492,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>421.5</v>
       </c>
       <c r="E3" t="n">
-        <v>299</v>
+        <v>310.17</v>
       </c>
       <c r="F3" t="n">
-        <v>239.24</v>
+        <v>180.93</v>
       </c>
       <c r="G3" t="n">
-        <v>139.55</v>
+        <v>731.67</v>
       </c>
       <c r="H3" t="n">
-        <v>538.24</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
+        <v>191.67</v>
       </c>
     </row>
     <row r="4">
@@ -535,31 +520,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B4" t="n">
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>398</v>
       </c>
       <c r="E4" t="n">
-        <v>252</v>
+        <v>318.47</v>
       </c>
       <c r="F4" t="n">
-        <v>285.5</v>
+        <v>185.78</v>
       </c>
       <c r="G4" t="n">
-        <v>166.54</v>
+        <v>716.47</v>
       </c>
       <c r="H4" t="n">
-        <v>537.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
+        <v>176.47</v>
       </c>
     </row>
     <row r="5">
@@ -568,31 +548,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B5" t="n">
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="E5" t="n">
-        <v>264</v>
+        <v>383.7</v>
       </c>
       <c r="F5" t="n">
-        <v>269.99</v>
+        <v>223.82</v>
       </c>
       <c r="G5" t="n">
-        <v>157.5</v>
+        <v>775.7</v>
       </c>
       <c r="H5" t="n">
-        <v>533.99</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
+        <v>235.7</v>
       </c>
     </row>
     <row r="6">
@@ -601,31 +576,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B6" t="n">
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>393</v>
       </c>
       <c r="E6" t="n">
-        <v>266</v>
+        <v>351.78</v>
       </c>
       <c r="F6" t="n">
-        <v>271.22</v>
+        <v>205.2</v>
       </c>
       <c r="G6" t="n">
-        <v>158.21</v>
+        <v>744.78</v>
       </c>
       <c r="H6" t="n">
-        <v>537.22</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
+        <v>204.78</v>
       </c>
     </row>
     <row r="7">
@@ -634,31 +604,26 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P01｜平鎮1</t>
-        </is>
+      <c r="B7" t="n">
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>402</v>
       </c>
       <c r="E7" t="n">
-        <v>264</v>
+        <v>391.66</v>
       </c>
       <c r="F7" t="n">
-        <v>274.58</v>
+        <v>228.47</v>
       </c>
       <c r="G7" t="n">
-        <v>160.17</v>
+        <v>793.66</v>
       </c>
       <c r="H7" t="n">
-        <v>538.58</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="8">
@@ -667,31 +632,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>332</v>
       </c>
       <c r="E8" t="n">
-        <v>248</v>
+        <v>396.91</v>
       </c>
       <c r="F8" t="n">
-        <v>289.61</v>
+        <v>231.53</v>
       </c>
       <c r="G8" t="n">
-        <v>168.94</v>
+        <v>728.91</v>
       </c>
       <c r="H8" t="n">
-        <v>537.61</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
+        <v>188.91</v>
       </c>
     </row>
     <row r="9">
@@ -700,31 +660,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>368</v>
       </c>
       <c r="E9" t="n">
-        <v>240</v>
+        <v>338.66</v>
       </c>
       <c r="F9" t="n">
-        <v>299.09</v>
+        <v>197.55</v>
       </c>
       <c r="G9" t="n">
-        <v>174.47</v>
+        <v>706.66</v>
       </c>
       <c r="H9" t="n">
-        <v>539.09</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
+        <v>166.66</v>
       </c>
     </row>
     <row r="10">
@@ -733,31 +688,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>365</v>
       </c>
       <c r="E10" t="n">
-        <v>272</v>
+        <v>419.55</v>
       </c>
       <c r="F10" t="n">
-        <v>267.12</v>
+        <v>244.74</v>
       </c>
       <c r="G10" t="n">
-        <v>155.82</v>
+        <v>784.55</v>
       </c>
       <c r="H10" t="n">
-        <v>539.12</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
+        <v>244.55</v>
       </c>
     </row>
     <row r="11">
@@ -766,31 +716,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B11" t="n">
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>392</v>
       </c>
       <c r="E11" t="n">
-        <v>248</v>
+        <v>333.45</v>
       </c>
       <c r="F11" t="n">
-        <v>291.33</v>
+        <v>194.51</v>
       </c>
       <c r="G11" t="n">
-        <v>169.94</v>
+        <v>725.45</v>
       </c>
       <c r="H11" t="n">
-        <v>539.33</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
+        <v>185.45</v>
       </c>
     </row>
     <row r="12">
@@ -799,31 +744,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B12" t="n">
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c r="E12" t="n">
-        <v>264</v>
+        <v>368.52</v>
       </c>
       <c r="F12" t="n">
-        <v>271.91</v>
+        <v>214.97</v>
       </c>
       <c r="G12" t="n">
-        <v>158.61</v>
+        <v>656.52</v>
       </c>
       <c r="H12" t="n">
-        <v>535.91</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
+        <v>116.52</v>
       </c>
     </row>
     <row r="13">
@@ -832,31 +772,26 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>P02｜平鎮2</t>
-        </is>
+      <c r="B13" t="n">
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E13" t="n">
-        <v>264</v>
+        <v>522.95</v>
       </c>
       <c r="F13" t="n">
-        <v>274.24</v>
+        <v>305.06</v>
       </c>
       <c r="G13" t="n">
-        <v>159.97</v>
+        <v>818.95</v>
       </c>
       <c r="H13" t="n">
-        <v>538.24</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
+        <v>278.95</v>
       </c>
     </row>
     <row r="14">
@@ -865,31 +800,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E14" t="n">
-        <v>256</v>
+        <v>406.84</v>
       </c>
       <c r="F14" t="n">
-        <v>281.73</v>
+        <v>237.33</v>
       </c>
       <c r="G14" t="n">
-        <v>164.34</v>
+        <v>710.84</v>
       </c>
       <c r="H14" t="n">
-        <v>537.73</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
+        <v>170.84</v>
       </c>
     </row>
     <row r="15">
@@ -898,31 +828,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>423</v>
       </c>
       <c r="E15" t="n">
-        <v>241</v>
+        <v>271.48</v>
       </c>
       <c r="F15" t="n">
-        <v>297.04</v>
+        <v>158.36</v>
       </c>
       <c r="G15" t="n">
-        <v>173.27</v>
+        <v>694.48</v>
       </c>
       <c r="H15" t="n">
-        <v>538.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+        <v>154.48</v>
       </c>
     </row>
     <row r="16">
@@ -931,31 +856,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>336</v>
       </c>
       <c r="E16" t="n">
-        <v>296</v>
+        <v>449.44</v>
       </c>
       <c r="F16" t="n">
-        <v>243.04</v>
+        <v>262.17</v>
       </c>
       <c r="G16" t="n">
-        <v>141.77</v>
+        <v>785.4400000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>539.04</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
+        <v>245.44</v>
       </c>
     </row>
     <row r="17">
@@ -964,31 +884,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B17" t="n">
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>362</v>
       </c>
       <c r="E17" t="n">
-        <v>296</v>
+        <v>325.84</v>
       </c>
       <c r="F17" t="n">
-        <v>242.04</v>
+        <v>190.07</v>
       </c>
       <c r="G17" t="n">
-        <v>141.19</v>
+        <v>687.84</v>
       </c>
       <c r="H17" t="n">
-        <v>538.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
+        <v>147.84</v>
       </c>
     </row>
     <row r="18">
@@ -997,31 +912,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B18" t="n">
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>363</v>
       </c>
       <c r="E18" t="n">
-        <v>328</v>
+        <v>405.24</v>
       </c>
       <c r="F18" t="n">
-        <v>211.97</v>
+        <v>236.39</v>
       </c>
       <c r="G18" t="n">
-        <v>123.65</v>
+        <v>768.24</v>
       </c>
       <c r="H18" t="n">
-        <v>539.97</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
+        <v>228.24</v>
       </c>
     </row>
     <row r="19">
@@ -1030,31 +940,26 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>P03｜平鎮3</t>
-        </is>
+      <c r="B19" t="n">
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>380</v>
       </c>
       <c r="E19" t="n">
-        <v>256</v>
+        <v>449.79</v>
       </c>
       <c r="F19" t="n">
-        <v>283.25</v>
+        <v>262.38</v>
       </c>
       <c r="G19" t="n">
-        <v>165.23</v>
+        <v>829.79</v>
       </c>
       <c r="H19" t="n">
-        <v>539.25</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
+        <v>289.79</v>
       </c>
     </row>
     <row r="20">
@@ -1063,31 +968,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="E20" t="n">
-        <v>272</v>
+        <v>426.62</v>
       </c>
       <c r="F20" t="n">
-        <v>265.3</v>
+        <v>248.86</v>
       </c>
       <c r="G20" t="n">
-        <v>154.76</v>
+        <v>754.62</v>
       </c>
       <c r="H20" t="n">
-        <v>537.3</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
+        <v>214.62</v>
       </c>
     </row>
     <row r="21">
@@ -1096,31 +996,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="E21" t="n">
-        <v>264</v>
+        <v>340.11</v>
       </c>
       <c r="F21" t="n">
-        <v>272.8</v>
+        <v>198.4</v>
       </c>
       <c r="G21" t="n">
-        <v>159.13</v>
+        <v>650.11</v>
       </c>
       <c r="H21" t="n">
-        <v>536.8</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
+        <v>110.11</v>
       </c>
     </row>
     <row r="22">
@@ -1129,31 +1024,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>385</v>
       </c>
       <c r="E22" t="n">
-        <v>294</v>
+        <v>539.75</v>
       </c>
       <c r="F22" t="n">
-        <v>240.57</v>
+        <v>314.85</v>
       </c>
       <c r="G22" t="n">
-        <v>140.33</v>
+        <v>924.75</v>
       </c>
       <c r="H22" t="n">
-        <v>534.5700000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
+        <v>384.75</v>
       </c>
     </row>
     <row r="23">
@@ -1162,31 +1052,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B23" t="n">
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="E23" t="n">
-        <v>284</v>
+        <v>377.65</v>
       </c>
       <c r="F23" t="n">
-        <v>253.42</v>
+        <v>220.29</v>
       </c>
       <c r="G23" t="n">
-        <v>147.83</v>
+        <v>689.65</v>
       </c>
       <c r="H23" t="n">
-        <v>537.42</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
+        <v>149.65</v>
       </c>
     </row>
     <row r="24">
@@ -1195,31 +1080,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B24" t="n">
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="E24" t="n">
-        <v>272</v>
+        <v>467.87</v>
       </c>
       <c r="F24" t="n">
-        <v>265.82</v>
+        <v>272.92</v>
       </c>
       <c r="G24" t="n">
-        <v>155.06</v>
+        <v>803.87</v>
       </c>
       <c r="H24" t="n">
-        <v>537.8200000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
+        <v>263.87</v>
       </c>
     </row>
     <row r="25">
@@ -1228,31 +1108,26 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>P04｜平鎮4</t>
-        </is>
+      <c r="B25" t="n">
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="E25" t="n">
-        <v>296</v>
+        <v>437.94</v>
       </c>
       <c r="F25" t="n">
-        <v>243.04</v>
+        <v>255.46</v>
       </c>
       <c r="G25" t="n">
-        <v>141.77</v>
+        <v>781.9400000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>539.04</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
+        <v>241.94</v>
       </c>
     </row>
     <row r="26">
@@ -1261,31 +1136,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="E26" t="n">
-        <v>284</v>
+        <v>487.94</v>
       </c>
       <c r="F26" t="n">
-        <v>255.83</v>
+        <v>284.63</v>
       </c>
       <c r="G26" t="n">
-        <v>149.23</v>
+        <v>811.9400000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>539.83</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
+        <v>271.94</v>
       </c>
     </row>
     <row r="27">
@@ -1294,31 +1164,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E27" t="n">
-        <v>260</v>
+        <v>381.39</v>
       </c>
       <c r="F27" t="n">
-        <v>279.82</v>
+        <v>222.48</v>
       </c>
       <c r="G27" t="n">
-        <v>163.23</v>
+        <v>721.39</v>
       </c>
       <c r="H27" t="n">
-        <v>539.8200000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
+        <v>181.39</v>
       </c>
     </row>
     <row r="28">
@@ -1327,31 +1192,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>352</v>
       </c>
       <c r="E28" t="n">
-        <v>324</v>
+        <v>386.28</v>
       </c>
       <c r="F28" t="n">
-        <v>212.89</v>
+        <v>225.33</v>
       </c>
       <c r="G28" t="n">
-        <v>124.19</v>
+        <v>738.28</v>
       </c>
       <c r="H28" t="n">
-        <v>536.89</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
+        <v>198.28</v>
       </c>
     </row>
     <row r="29">
@@ -1360,31 +1220,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B29" t="n">
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>352</v>
       </c>
       <c r="E29" t="n">
-        <v>280</v>
+        <v>334.85</v>
       </c>
       <c r="F29" t="n">
-        <v>257.09</v>
+        <v>195.33</v>
       </c>
       <c r="G29" t="n">
-        <v>149.97</v>
+        <v>686.85</v>
       </c>
       <c r="H29" t="n">
-        <v>537.09</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
+        <v>146.85</v>
       </c>
     </row>
     <row r="30">
@@ -1393,31 +1248,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B30" t="n">
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>400</v>
       </c>
       <c r="E30" t="n">
-        <v>296</v>
+        <v>412.29</v>
       </c>
       <c r="F30" t="n">
-        <v>242.32</v>
+        <v>240.5</v>
       </c>
       <c r="G30" t="n">
-        <v>141.35</v>
+        <v>812.29</v>
       </c>
       <c r="H30" t="n">
-        <v>538.3200000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
+        <v>272.29</v>
       </c>
     </row>
     <row r="31">
@@ -1426,31 +1276,26 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>P05｜平鎮5</t>
-        </is>
+      <c r="B31" t="n">
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>368</v>
       </c>
       <c r="E31" t="n">
-        <v>280</v>
+        <v>432.13</v>
       </c>
       <c r="F31" t="n">
-        <v>258.98</v>
+        <v>252.07</v>
       </c>
       <c r="G31" t="n">
-        <v>151.07</v>
+        <v>800.13</v>
       </c>
       <c r="H31" t="n">
-        <v>538.98</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
+        <v>260.13</v>
       </c>
     </row>
     <row r="32">
@@ -1459,31 +1304,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>410</v>
       </c>
       <c r="E32" t="n">
-        <v>280</v>
+        <v>303.92</v>
       </c>
       <c r="F32" t="n">
-        <v>259.98</v>
+        <v>177.29</v>
       </c>
       <c r="G32" t="n">
-        <v>151.66</v>
+        <v>713.92</v>
       </c>
       <c r="H32" t="n">
-        <v>539.98</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
+        <v>173.92</v>
       </c>
     </row>
     <row r="33">
@@ -1492,31 +1332,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>406.5</v>
       </c>
       <c r="E33" t="n">
-        <v>256</v>
+        <v>504.96</v>
       </c>
       <c r="F33" t="n">
-        <v>283.22</v>
+        <v>294.56</v>
       </c>
       <c r="G33" t="n">
-        <v>165.21</v>
+        <v>911.46</v>
       </c>
       <c r="H33" t="n">
-        <v>539.22</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
+        <v>371.46</v>
       </c>
     </row>
     <row r="34">
@@ -1525,31 +1360,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>307</v>
       </c>
       <c r="E34" t="n">
-        <v>264</v>
+        <v>390.1</v>
       </c>
       <c r="F34" t="n">
-        <v>273.93</v>
+        <v>227.56</v>
       </c>
       <c r="G34" t="n">
-        <v>159.79</v>
+        <v>697.1</v>
       </c>
       <c r="H34" t="n">
-        <v>537.9299999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
+        <v>157.1</v>
       </c>
     </row>
     <row r="35">
@@ -1558,31 +1388,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>304</v>
       </c>
       <c r="E35" t="n">
-        <v>296</v>
+        <v>360.04</v>
       </c>
       <c r="F35" t="n">
-        <v>243.81</v>
+        <v>210.03</v>
       </c>
       <c r="G35" t="n">
-        <v>142.22</v>
+        <v>664.04</v>
       </c>
       <c r="H35" t="n">
-        <v>539.8099999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
+        <v>124.04</v>
       </c>
     </row>
     <row r="36">
@@ -1591,31 +1416,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B36" t="n">
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="E36" t="n">
-        <v>296</v>
+        <v>328.27</v>
       </c>
       <c r="F36" t="n">
-        <v>242.27</v>
+        <v>191.49</v>
       </c>
       <c r="G36" t="n">
-        <v>141.33</v>
+        <v>642.27</v>
       </c>
       <c r="H36" t="n">
-        <v>538.27</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
+        <v>102.27</v>
       </c>
     </row>
     <row r="37">
@@ -1624,31 +1444,26 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>P06｜平鎮6</t>
-        </is>
+      <c r="B37" t="n">
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="E37" t="n">
-        <v>296</v>
+        <v>359.97</v>
       </c>
       <c r="F37" t="n">
-        <v>237.06</v>
+        <v>209.98</v>
       </c>
       <c r="G37" t="n">
-        <v>138.29</v>
+        <v>745.97</v>
       </c>
       <c r="H37" t="n">
-        <v>533.0599999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
+        <v>205.97</v>
       </c>
     </row>
     <row r="38">
@@ -1657,31 +1472,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B38" t="n">
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>323</v>
       </c>
       <c r="E38" t="n">
-        <v>272</v>
+        <v>375.7</v>
       </c>
       <c r="F38" t="n">
-        <v>264.82</v>
+        <v>219.16</v>
       </c>
       <c r="G38" t="n">
-        <v>154.48</v>
+        <v>698.7</v>
       </c>
       <c r="H38" t="n">
-        <v>536.8200000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
+        <v>158.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,31 +1500,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B39" t="n">
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="E39" t="n">
-        <v>257</v>
+        <v>331.5</v>
       </c>
       <c r="F39" t="n">
-        <v>280.2</v>
+        <v>193.38</v>
       </c>
       <c r="G39" t="n">
-        <v>163.45</v>
+        <v>731.5</v>
       </c>
       <c r="H39" t="n">
-        <v>537.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="40">
@@ -1723,31 +1528,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B40" t="n">
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D40" t="n">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="E40" t="n">
-        <v>261</v>
+        <v>439.17</v>
       </c>
       <c r="F40" t="n">
-        <v>268.03</v>
+        <v>256.18</v>
       </c>
       <c r="G40" t="n">
-        <v>156.35</v>
+        <v>736.17</v>
       </c>
       <c r="H40" t="n">
-        <v>529.03</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
+        <v>196.17</v>
       </c>
     </row>
     <row r="41">
@@ -1756,31 +1556,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B41" t="n">
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>22</v>
+        <v>350</v>
       </c>
       <c r="E41" t="n">
-        <v>240</v>
+        <v>401.74</v>
       </c>
       <c r="F41" t="n">
-        <v>296.74</v>
+        <v>234.35</v>
       </c>
       <c r="G41" t="n">
-        <v>173.1</v>
+        <v>751.74</v>
       </c>
       <c r="H41" t="n">
-        <v>536.74</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
+        <v>211.74</v>
       </c>
     </row>
     <row r="42">
@@ -1789,31 +1584,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B42" t="n">
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
-        <v>24</v>
+        <v>335</v>
       </c>
       <c r="E42" t="n">
-        <v>263</v>
+        <v>370.32</v>
       </c>
       <c r="F42" t="n">
-        <v>275.21</v>
+        <v>216.02</v>
       </c>
       <c r="G42" t="n">
-        <v>160.54</v>
+        <v>705.3200000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>538.21</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
+        <v>165.32</v>
       </c>
     </row>
     <row r="43">
@@ -1822,31 +1612,26 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>P07｜平鎮7</t>
-        </is>
+      <c r="B43" t="n">
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="E43" t="n">
-        <v>240</v>
+        <v>393.64</v>
       </c>
       <c r="F43" t="n">
-        <v>298.75</v>
+        <v>229.62</v>
       </c>
       <c r="G43" t="n">
-        <v>174.27</v>
+        <v>793.64</v>
       </c>
       <c r="H43" t="n">
-        <v>538.75</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
+        <v>253.64</v>
       </c>
     </row>
     <row r="44">
@@ -1855,31 +1640,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B44" t="n">
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D44" t="n">
-        <v>22</v>
+        <v>408</v>
       </c>
       <c r="E44" t="n">
-        <v>256</v>
+        <v>327.37</v>
       </c>
       <c r="F44" t="n">
-        <v>282.24</v>
+        <v>190.97</v>
       </c>
       <c r="G44" t="n">
-        <v>164.64</v>
+        <v>735.37</v>
       </c>
       <c r="H44" t="n">
-        <v>538.24</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
+        <v>195.37</v>
       </c>
     </row>
     <row r="45">
@@ -1888,31 +1668,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B45" t="n">
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>24</v>
+        <v>370</v>
       </c>
       <c r="E45" t="n">
-        <v>312</v>
+        <v>453.86</v>
       </c>
       <c r="F45" t="n">
-        <v>227.28</v>
+        <v>264.75</v>
       </c>
       <c r="G45" t="n">
-        <v>132.58</v>
+        <v>823.86</v>
       </c>
       <c r="H45" t="n">
-        <v>539.28</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
+        <v>283.86</v>
       </c>
     </row>
     <row r="46">
@@ -1921,31 +1696,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B46" t="n">
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>368</v>
       </c>
       <c r="E46" t="n">
-        <v>272</v>
+        <v>324.79</v>
       </c>
       <c r="F46" t="n">
-        <v>264.26</v>
+        <v>189.46</v>
       </c>
       <c r="G46" t="n">
-        <v>154.15</v>
+        <v>692.79</v>
       </c>
       <c r="H46" t="n">
-        <v>536.26</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
+        <v>152.79</v>
       </c>
     </row>
     <row r="47">
@@ -1954,31 +1724,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B47" t="n">
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>336</v>
       </c>
       <c r="E47" t="n">
-        <v>272</v>
+        <v>381.11</v>
       </c>
       <c r="F47" t="n">
-        <v>261.83</v>
+        <v>222.32</v>
       </c>
       <c r="G47" t="n">
-        <v>152.73</v>
+        <v>717.11</v>
       </c>
       <c r="H47" t="n">
-        <v>533.83</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
+        <v>177.11</v>
       </c>
     </row>
     <row r="48">
@@ -1987,31 +1752,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B48" t="n">
+        <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
-        <v>23</v>
+        <v>344</v>
       </c>
       <c r="E48" t="n">
-        <v>248</v>
+        <v>394.76</v>
       </c>
       <c r="F48" t="n">
-        <v>283.58</v>
+        <v>230.28</v>
       </c>
       <c r="G48" t="n">
-        <v>165.42</v>
+        <v>738.76</v>
       </c>
       <c r="H48" t="n">
-        <v>531.58</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
+        <v>198.76</v>
       </c>
     </row>
     <row r="49">
@@ -2020,31 +1780,26 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P08｜平鎮8</t>
-        </is>
+      <c r="B49" t="n">
+        <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="E49" t="n">
-        <v>224</v>
+        <v>362.95</v>
       </c>
       <c r="F49" t="n">
-        <v>313.93</v>
+        <v>211.72</v>
       </c>
       <c r="G49" t="n">
-        <v>183.12</v>
+        <v>735.95</v>
       </c>
       <c r="H49" t="n">
-        <v>537.9299999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
+        <v>195.95</v>
       </c>
     </row>
     <row r="50">
@@ -2053,31 +1808,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B50" t="n">
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D50" t="n">
-        <v>25</v>
+        <v>344</v>
       </c>
       <c r="E50" t="n">
-        <v>272</v>
+        <v>335.82</v>
       </c>
       <c r="F50" t="n">
-        <v>261.83</v>
+        <v>195.9</v>
       </c>
       <c r="G50" t="n">
-        <v>152.74</v>
+        <v>679.8200000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>533.83</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
+        <v>139.82</v>
       </c>
     </row>
     <row r="51">
@@ -2086,31 +1836,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B51" t="n">
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D51" t="n">
-        <v>22</v>
+        <v>312</v>
       </c>
       <c r="E51" t="n">
-        <v>246</v>
+        <v>547</v>
       </c>
       <c r="F51" t="n">
-        <v>292.59</v>
+        <v>319.08</v>
       </c>
       <c r="G51" t="n">
-        <v>170.68</v>
+        <v>859</v>
       </c>
       <c r="H51" t="n">
-        <v>538.59</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52">
@@ -2119,31 +1864,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B52" t="n">
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D52" t="n">
-        <v>23</v>
+        <v>272</v>
       </c>
       <c r="E52" t="n">
-        <v>256</v>
+        <v>385.36</v>
       </c>
       <c r="F52" t="n">
-        <v>269.04</v>
+        <v>224.79</v>
       </c>
       <c r="G52" t="n">
-        <v>156.94</v>
+        <v>657.36</v>
       </c>
       <c r="H52" t="n">
-        <v>525.04</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
+        <v>117.36</v>
       </c>
     </row>
     <row r="53">
@@ -2152,31 +1892,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B53" t="n">
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D53" t="n">
-        <v>23</v>
+        <v>386</v>
       </c>
       <c r="E53" t="n">
-        <v>256</v>
+        <v>496.77</v>
       </c>
       <c r="F53" t="n">
-        <v>282.05</v>
+        <v>289.78</v>
       </c>
       <c r="G53" t="n">
-        <v>164.53</v>
+        <v>882.77</v>
       </c>
       <c r="H53" t="n">
-        <v>538.05</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
+        <v>342.77</v>
       </c>
     </row>
     <row r="54">
@@ -2185,31 +1920,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B54" t="n">
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="E54" t="n">
-        <v>244</v>
+        <v>405.59</v>
       </c>
       <c r="F54" t="n">
-        <v>295.13</v>
+        <v>236.59</v>
       </c>
       <c r="G54" t="n">
-        <v>172.16</v>
+        <v>707.59</v>
       </c>
       <c r="H54" t="n">
-        <v>539.13</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
+        <v>167.59</v>
       </c>
     </row>
     <row r="55">
@@ -2218,31 +1948,26 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P09｜平鎮9</t>
-        </is>
+      <c r="B55" t="n">
+        <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
-        <v>22</v>
+        <v>292</v>
       </c>
       <c r="E55" t="n">
-        <v>248</v>
+        <v>427.95</v>
       </c>
       <c r="F55" t="n">
-        <v>287.67</v>
+        <v>249.64</v>
       </c>
       <c r="G55" t="n">
-        <v>167.81</v>
+        <v>719.95</v>
       </c>
       <c r="H55" t="n">
-        <v>535.67</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
+        <v>179.95</v>
       </c>
     </row>
     <row r="56">
@@ -2251,31 +1976,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B56" t="n">
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D56" t="n">
-        <v>22</v>
+        <v>355</v>
       </c>
       <c r="E56" t="n">
-        <v>243.5</v>
+        <v>357.37</v>
       </c>
       <c r="F56" t="n">
-        <v>292.25</v>
+        <v>208.47</v>
       </c>
       <c r="G56" t="n">
-        <v>170.48</v>
+        <v>712.37</v>
       </c>
       <c r="H56" t="n">
-        <v>535.75</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
+        <v>172.37</v>
       </c>
     </row>
     <row r="57">
@@ -2284,31 +2004,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B57" t="n">
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>362.5</v>
       </c>
       <c r="E57" t="n">
-        <v>248</v>
+        <v>335.68</v>
       </c>
       <c r="F57" t="n">
-        <v>287.83</v>
+        <v>195.82</v>
       </c>
       <c r="G57" t="n">
-        <v>167.9</v>
+        <v>698.1799999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>535.83</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
+        <v>158.18</v>
       </c>
     </row>
     <row r="58">
@@ -2317,31 +2032,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B58" t="n">
+        <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="E58" t="n">
-        <v>277</v>
+        <v>396.63</v>
       </c>
       <c r="F58" t="n">
-        <v>246.19</v>
+        <v>231.37</v>
       </c>
       <c r="G58" t="n">
-        <v>143.61</v>
+        <v>686.63</v>
       </c>
       <c r="H58" t="n">
-        <v>523.1900000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="59">
@@ -2350,31 +2060,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B59" t="n">
+        <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="E59" t="n">
-        <v>256</v>
+        <v>358.61</v>
       </c>
       <c r="F59" t="n">
-        <v>273.82</v>
+        <v>209.19</v>
       </c>
       <c r="G59" t="n">
-        <v>159.73</v>
+        <v>680.61</v>
       </c>
       <c r="H59" t="n">
-        <v>529.8200000000001</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
+        <v>140.61</v>
       </c>
     </row>
     <row r="60">
@@ -2383,31 +2088,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B60" t="n">
+        <v>5</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D60" t="n">
-        <v>22</v>
+        <v>281</v>
       </c>
       <c r="E60" t="n">
-        <v>283</v>
+        <v>606.4</v>
       </c>
       <c r="F60" t="n">
-        <v>252.72</v>
+        <v>353.73</v>
       </c>
       <c r="G60" t="n">
-        <v>147.42</v>
+        <v>887.4</v>
       </c>
       <c r="H60" t="n">
-        <v>535.72</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
+        <v>347.4</v>
       </c>
     </row>
     <row r="61">
@@ -2416,31 +2116,26 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P10｜平鎮10</t>
-        </is>
+      <c r="B61" t="n">
+        <v>6</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E61" t="n">
-        <v>248</v>
+        <v>351.54</v>
       </c>
       <c r="F61" t="n">
-        <v>288.5</v>
+        <v>205.06</v>
       </c>
       <c r="G61" t="n">
-        <v>168.29</v>
+        <v>667.54</v>
       </c>
       <c r="H61" t="n">
-        <v>536.5</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
+        <v>127.54</v>
       </c>
     </row>
     <row r="62">
@@ -2449,31 +2144,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B62" t="n">
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>392</v>
       </c>
       <c r="E62" t="n">
-        <v>272</v>
+        <v>337.33</v>
       </c>
       <c r="F62" t="n">
-        <v>266.31</v>
+        <v>196.78</v>
       </c>
       <c r="G62" t="n">
-        <v>155.35</v>
+        <v>729.33</v>
       </c>
       <c r="H62" t="n">
-        <v>538.3099999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
+        <v>189.33</v>
       </c>
     </row>
     <row r="63">
@@ -2482,31 +2172,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B63" t="n">
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D63" t="n">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="E63" t="n">
-        <v>280</v>
+        <v>430.57</v>
       </c>
       <c r="F63" t="n">
-        <v>258.4</v>
+        <v>251.17</v>
       </c>
       <c r="G63" t="n">
-        <v>150.73</v>
+        <v>755.5700000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>538.4</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
+        <v>215.57</v>
       </c>
     </row>
     <row r="64">
@@ -2515,31 +2200,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B64" t="n">
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>320</v>
       </c>
       <c r="E64" t="n">
-        <v>216</v>
+        <v>400.64</v>
       </c>
       <c r="F64" t="n">
-        <v>321.17</v>
+        <v>233.71</v>
       </c>
       <c r="G64" t="n">
-        <v>187.35</v>
+        <v>720.64</v>
       </c>
       <c r="H64" t="n">
-        <v>537.17</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="65">
@@ -2548,31 +2228,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B65" t="n">
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>376</v>
       </c>
       <c r="E65" t="n">
-        <v>256</v>
+        <v>309.09</v>
       </c>
       <c r="F65" t="n">
-        <v>283.77</v>
+        <v>180.3</v>
       </c>
       <c r="G65" t="n">
-        <v>165.53</v>
+        <v>685.09</v>
       </c>
       <c r="H65" t="n">
-        <v>539.77</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
+        <v>145.09</v>
       </c>
     </row>
     <row r="66">
@@ -2581,31 +2256,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B66" t="n">
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="E66" t="n">
-        <v>264</v>
+        <v>334.58</v>
       </c>
       <c r="F66" t="n">
-        <v>275.38</v>
+        <v>195.17</v>
       </c>
       <c r="G66" t="n">
-        <v>160.64</v>
+        <v>726.58</v>
       </c>
       <c r="H66" t="n">
-        <v>539.38</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
+        <v>186.58</v>
       </c>
     </row>
     <row r="67">
@@ -2614,31 +2284,26 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P11｜平鎮11</t>
-        </is>
+      <c r="B67" t="n">
+        <v>6</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D67" t="n">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="E67" t="n">
-        <v>248</v>
+        <v>400.96</v>
       </c>
       <c r="F67" t="n">
-        <v>288.52</v>
+        <v>233.89</v>
       </c>
       <c r="G67" t="n">
-        <v>168.3</v>
+        <v>752.96</v>
       </c>
       <c r="H67" t="n">
-        <v>536.52</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
+        <v>212.96</v>
       </c>
     </row>
     <row r="68">
@@ -2647,31 +2312,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B68" t="n">
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D68" t="n">
-        <v>25</v>
+        <v>352</v>
       </c>
       <c r="E68" t="n">
-        <v>296</v>
+        <v>560.65</v>
       </c>
       <c r="F68" t="n">
-        <v>243.31</v>
+        <v>327.05</v>
       </c>
       <c r="G68" t="n">
-        <v>141.93</v>
+        <v>912.65</v>
       </c>
       <c r="H68" t="n">
-        <v>539.3099999999999</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
+        <v>372.65</v>
       </c>
     </row>
     <row r="69">
@@ -2680,31 +2340,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B69" t="n">
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D69" t="n">
-        <v>23</v>
+        <v>383</v>
       </c>
       <c r="E69" t="n">
-        <v>264</v>
+        <v>368.64</v>
       </c>
       <c r="F69" t="n">
-        <v>274.44</v>
+        <v>215.04</v>
       </c>
       <c r="G69" t="n">
-        <v>160.09</v>
+        <v>751.64</v>
       </c>
       <c r="H69" t="n">
-        <v>538.4400000000001</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
+        <v>211.64</v>
       </c>
     </row>
     <row r="70">
@@ -2713,31 +2368,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B70" t="n">
+        <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="E70" t="n">
-        <v>247</v>
+        <v>371.08</v>
       </c>
       <c r="F70" t="n">
-        <v>287.91</v>
+        <v>216.47</v>
       </c>
       <c r="G70" t="n">
-        <v>167.95</v>
+        <v>732.08</v>
       </c>
       <c r="H70" t="n">
-        <v>534.91</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
+        <v>192.08</v>
       </c>
     </row>
     <row r="71">
@@ -2746,31 +2396,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B71" t="n">
+        <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D71" t="n">
-        <v>24</v>
+        <v>339</v>
       </c>
       <c r="E71" t="n">
-        <v>292</v>
+        <v>372.09</v>
       </c>
       <c r="F71" t="n">
-        <v>241.48</v>
+        <v>217.05</v>
       </c>
       <c r="G71" t="n">
-        <v>140.86</v>
+        <v>711.09</v>
       </c>
       <c r="H71" t="n">
-        <v>533.48</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
+        <v>171.09</v>
       </c>
     </row>
     <row r="72">
@@ -2779,31 +2424,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B72" t="n">
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D72" t="n">
-        <v>22</v>
+        <v>346</v>
       </c>
       <c r="E72" t="n">
-        <v>234</v>
+        <v>432.58</v>
       </c>
       <c r="F72" t="n">
-        <v>303.7</v>
+        <v>252.34</v>
       </c>
       <c r="G72" t="n">
-        <v>177.16</v>
+        <v>778.58</v>
       </c>
       <c r="H72" t="n">
-        <v>537.7</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
+        <v>238.58</v>
       </c>
     </row>
     <row r="73">
@@ -2812,31 +2452,26 @@
           <t>P12</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P12｜平鎮12</t>
-        </is>
+      <c r="B73" t="n">
+        <v>6</v>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D73" t="n">
-        <v>22</v>
+        <v>344</v>
       </c>
       <c r="E73" t="n">
-        <v>257</v>
+        <v>344.28</v>
       </c>
       <c r="F73" t="n">
-        <v>274.3</v>
+        <v>200.83</v>
       </c>
       <c r="G73" t="n">
-        <v>160.01</v>
+        <v>688.28</v>
       </c>
       <c r="H73" t="n">
-        <v>531.3</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
+        <v>148.28</v>
       </c>
     </row>
     <row r="74">
@@ -2845,30 +2480,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B74" t="n">
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E74" t="n">
-        <v>296</v>
+        <v>205.65</v>
       </c>
       <c r="F74" t="n">
-        <v>102.9</v>
+        <v>119.96</v>
       </c>
       <c r="G74" t="n">
-        <v>60.02</v>
+        <v>477.65</v>
       </c>
       <c r="H74" t="n">
-        <v>398.9</v>
-      </c>
-      <c r="I74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2878,30 +2508,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B75" t="n">
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D75" t="n">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="E75" t="n">
-        <v>270</v>
+        <v>240.3</v>
       </c>
       <c r="F75" t="n">
-        <v>135.44</v>
+        <v>140.18</v>
       </c>
       <c r="G75" t="n">
-        <v>79.01000000000001</v>
+        <v>494.3</v>
       </c>
       <c r="H75" t="n">
-        <v>405.44</v>
-      </c>
-      <c r="I75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2911,30 +2536,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B76" t="n">
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D76" t="n">
-        <v>16</v>
+        <v>216</v>
       </c>
       <c r="E76" t="n">
-        <v>216</v>
+        <v>237.69</v>
       </c>
       <c r="F76" t="n">
-        <v>158.84</v>
+        <v>138.66</v>
       </c>
       <c r="G76" t="n">
-        <v>92.65000000000001</v>
+        <v>453.69</v>
       </c>
       <c r="H76" t="n">
-        <v>374.84</v>
-      </c>
-      <c r="I76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2944,30 +2564,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B77" t="n">
+        <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="E77" t="n">
-        <v>168</v>
+        <v>223.23</v>
       </c>
       <c r="F77" t="n">
-        <v>213.31</v>
+        <v>130.22</v>
       </c>
       <c r="G77" t="n">
-        <v>124.43</v>
+        <v>423.23</v>
       </c>
       <c r="H77" t="n">
-        <v>381.31</v>
-      </c>
-      <c r="I77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2977,30 +2592,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B78" t="n">
+        <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="E78" t="n">
-        <v>192</v>
+        <v>209.71</v>
       </c>
       <c r="F78" t="n">
-        <v>204.78</v>
+        <v>122.33</v>
       </c>
       <c r="G78" t="n">
-        <v>119.46</v>
+        <v>420.71</v>
       </c>
       <c r="H78" t="n">
-        <v>396.78</v>
-      </c>
-      <c r="I78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3010,30 +2620,25 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>W01｜五股1</t>
-        </is>
+      <c r="B79" t="n">
+        <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D79" t="n">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="E79" t="n">
-        <v>272</v>
+        <v>245.97</v>
       </c>
       <c r="F79" t="n">
-        <v>133.21</v>
+        <v>143.48</v>
       </c>
       <c r="G79" t="n">
-        <v>77.70999999999999</v>
+        <v>437.97</v>
       </c>
       <c r="H79" t="n">
-        <v>405.21</v>
-      </c>
-      <c r="I79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3043,30 +2648,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B80" t="n">
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D80" t="n">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="E80" t="n">
-        <v>200</v>
+        <v>236.84</v>
       </c>
       <c r="F80" t="n">
-        <v>194.25</v>
+        <v>138.16</v>
       </c>
       <c r="G80" t="n">
-        <v>113.31</v>
+        <v>452.84</v>
       </c>
       <c r="H80" t="n">
-        <v>394.25</v>
-      </c>
-      <c r="I80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3076,30 +2676,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B81" t="n">
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D81" t="n">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="E81" t="n">
-        <v>216</v>
+        <v>262.46</v>
       </c>
       <c r="F81" t="n">
-        <v>179.63</v>
+        <v>153.1</v>
       </c>
       <c r="G81" t="n">
-        <v>104.78</v>
+        <v>454.46</v>
       </c>
       <c r="H81" t="n">
-        <v>395.63</v>
-      </c>
-      <c r="I81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3109,30 +2704,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B82" t="n">
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D82" t="n">
-        <v>17</v>
+        <v>239</v>
       </c>
       <c r="E82" t="n">
-        <v>207</v>
+        <v>220.08</v>
       </c>
       <c r="F82" t="n">
-        <v>196</v>
+        <v>128.38</v>
       </c>
       <c r="G82" t="n">
-        <v>114.33</v>
+        <v>459.08</v>
       </c>
       <c r="H82" t="n">
-        <v>403</v>
-      </c>
-      <c r="I82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3142,30 +2732,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B83" t="n">
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D83" t="n">
-        <v>16</v>
+        <v>216</v>
       </c>
       <c r="E83" t="n">
-        <v>201</v>
+        <v>274.78</v>
       </c>
       <c r="F83" t="n">
-        <v>194.95</v>
+        <v>160.29</v>
       </c>
       <c r="G83" t="n">
-        <v>113.72</v>
+        <v>490.78</v>
       </c>
       <c r="H83" t="n">
-        <v>395.95</v>
-      </c>
-      <c r="I83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3175,30 +2760,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B84" t="n">
+        <v>5</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D84" t="n">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="E84" t="n">
-        <v>192</v>
+        <v>215.65</v>
       </c>
       <c r="F84" t="n">
-        <v>211.88</v>
+        <v>125.8</v>
       </c>
       <c r="G84" t="n">
-        <v>123.6</v>
+        <v>397.65</v>
       </c>
       <c r="H84" t="n">
-        <v>403.88</v>
-      </c>
-      <c r="I84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3208,30 +2788,25 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
+      <c r="B85" t="n">
+        <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D85" t="n">
-        <v>16</v>
+        <v>232</v>
       </c>
       <c r="E85" t="n">
-        <v>192</v>
+        <v>221.24</v>
       </c>
       <c r="F85" t="n">
-        <v>205.83</v>
+        <v>129.06</v>
       </c>
       <c r="G85" t="n">
-        <v>120.07</v>
+        <v>453.24</v>
       </c>
       <c r="H85" t="n">
-        <v>397.83</v>
-      </c>
-      <c r="I85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Daily_Route_Summary_cross.xlsx
+++ b/output/Daily_Route_Summary_cross.xlsx
@@ -692,22 +692,22 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E10" t="n">
-        <v>419.55</v>
+        <v>404.64</v>
       </c>
       <c r="F10" t="n">
-        <v>244.74</v>
+        <v>236.04</v>
       </c>
       <c r="G10" t="n">
-        <v>784.55</v>
+        <v>766.64</v>
       </c>
       <c r="H10" t="n">
-        <v>244.55</v>
+        <v>226.64</v>
       </c>
     </row>
     <row r="11">
@@ -1336,22 +1336,22 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>406.5</v>
+        <v>403.5</v>
       </c>
       <c r="E33" t="n">
-        <v>504.96</v>
+        <v>357.11</v>
       </c>
       <c r="F33" t="n">
-        <v>294.56</v>
+        <v>208.31</v>
       </c>
       <c r="G33" t="n">
-        <v>911.46</v>
+        <v>760.61</v>
       </c>
       <c r="H33" t="n">
-        <v>371.46</v>
+        <v>220.61</v>
       </c>
     </row>
     <row r="34">

--- a/output/Daily_Route_Summary_cross.xlsx
+++ b/output/Daily_Route_Summary_cross.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>driver</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>stop_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>service_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>drive_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dist_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>total_min</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overtime_min</t>
         </is>
@@ -2484,19 +2496,19 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D74" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E74" t="n">
-        <v>205.65</v>
+        <v>231.65</v>
       </c>
       <c r="F74" t="n">
-        <v>119.96</v>
+        <v>135.13</v>
       </c>
       <c r="G74" t="n">
-        <v>477.65</v>
+        <v>505.65</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2540,19 +2552,19 @@
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D76" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E76" t="n">
-        <v>237.69</v>
+        <v>249.89</v>
       </c>
       <c r="F76" t="n">
-        <v>138.66</v>
+        <v>145.77</v>
       </c>
       <c r="G76" t="n">
-        <v>453.69</v>
+        <v>468.89</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2624,19 +2636,19 @@
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D79" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E79" t="n">
-        <v>245.97</v>
+        <v>249.43</v>
       </c>
       <c r="F79" t="n">
-        <v>143.48</v>
+        <v>145.5</v>
       </c>
       <c r="G79" t="n">
-        <v>437.97</v>
+        <v>443.43</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>

--- a/output/Daily_Route_Summary_cross.xlsx
+++ b/output/Daily_Route_Summary_cross.xlsx
@@ -2496,19 +2496,19 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D74" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E74" t="n">
-        <v>231.65</v>
+        <v>205.65</v>
       </c>
       <c r="F74" t="n">
-        <v>135.13</v>
+        <v>119.96</v>
       </c>
       <c r="G74" t="n">
-        <v>505.65</v>
+        <v>477.65</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2552,19 +2552,19 @@
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D76" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E76" t="n">
-        <v>249.89</v>
+        <v>237.69</v>
       </c>
       <c r="F76" t="n">
-        <v>145.77</v>
+        <v>138.66</v>
       </c>
       <c r="G76" t="n">
-        <v>468.89</v>
+        <v>453.69</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2636,19 +2636,19 @@
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D79" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E79" t="n">
-        <v>249.43</v>
+        <v>245.97</v>
       </c>
       <c r="F79" t="n">
-        <v>145.5</v>
+        <v>143.48</v>
       </c>
       <c r="G79" t="n">
-        <v>443.43</v>
+        <v>437.97</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>

--- a/output/Daily_Route_Summary_cross.xlsx
+++ b/output/Daily_Route_Summary_cross.xlsx
@@ -2496,19 +2496,19 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D74" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E74" t="n">
-        <v>205.65</v>
+        <v>231.65</v>
       </c>
       <c r="F74" t="n">
-        <v>119.96</v>
+        <v>135.13</v>
       </c>
       <c r="G74" t="n">
-        <v>477.65</v>
+        <v>505.65</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2552,19 +2552,19 @@
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D76" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E76" t="n">
-        <v>237.69</v>
+        <v>249.89</v>
       </c>
       <c r="F76" t="n">
-        <v>138.66</v>
+        <v>145.77</v>
       </c>
       <c r="G76" t="n">
-        <v>453.69</v>
+        <v>468.89</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2636,19 +2636,19 @@
         <v>6</v>
       </c>
       <c r="C79" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D79" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E79" t="n">
-        <v>245.97</v>
+        <v>249.43</v>
       </c>
       <c r="F79" t="n">
-        <v>143.48</v>
+        <v>145.5</v>
       </c>
       <c r="G79" t="n">
-        <v>437.97</v>
+        <v>443.43</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
